--- a/docs/kofi-files/pack-cleaning/house-cleaning.xlsx
+++ b/docs/kofi-files/pack-cleaning/house-cleaning.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,16 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="001E5B3E"/>
+      <sz val="13"/>
+    </font>
+    <font>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
@@ -75,13 +86,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,4 +594,141 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>The numbers behind this list (2026 US, sourced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>This list</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026 US band</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Standard clean</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>$180</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>$120–280</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>HomeGuide; Housecall Pro; Thumbtack</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Deep clean</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>$325</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>$200–450</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Eufy; Angi; HomeGuide</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Move-out clean</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>$400</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>$200–600</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>HireAHelper; HomeGuide; Angi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Hourly per cleaner</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>$25–80</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>HomeGuide; CottageCare</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>